--- a/inst/simple_summ_plot/quarterly_summary_anthro.xlsx
+++ b/inst/simple_summ_plot/quarterly_summary_anthro.xlsx
@@ -500,19 +500,19 @@
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>0.215006983231782</v>
+        <v>0.215166419873943</v>
       </c>
       <c r="D2" t="n">
         <v>25.1770493728245</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0015947354417</v>
+        <v>15.0055258132617</v>
       </c>
       <c r="F2" t="n">
-        <v>56.0436597545318</v>
+        <v>56.0390455010563</v>
       </c>
       <c r="G2" t="n">
-        <v>20.5887388586068</v>
+        <v>20.5871039898867</v>
       </c>
       <c r="H2" t="n">
         <v>97</v>
@@ -521,19 +521,19 @@
         <v>84.1174762686931</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.000865226242053693</v>
+        <v>-0.000876888656503857</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0153959280979556</v>
+        <v>0.0153959280979592</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0379375167600715</v>
+        <v>-0.0383065390992723</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0830326023883536</v>
+        <v>0.0834792399499484</v>
       </c>
       <c r="N2" t="n">
-        <v>0.029419147671609</v>
+        <v>0.0295773951069833</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -557,19 +557,19 @@
         <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>0.228295176172521</v>
+        <v>0.228721469337774</v>
       </c>
       <c r="D3" t="n">
         <v>25.3702404861989</v>
       </c>
       <c r="E3" t="n">
-        <v>16.4005871007124</v>
+        <v>16.4311510169029</v>
       </c>
       <c r="F3" t="n">
-        <v>55.3810106637324</v>
+        <v>55.3504467475419</v>
       </c>
       <c r="G3" t="n">
-        <v>20.3539567260957</v>
+        <v>20.3431276741574</v>
       </c>
       <c r="H3" t="n">
         <v>96.3845432316923</v>
@@ -578,19 +578,19 @@
         <v>88.7761077748585</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00168797891412169</v>
+        <v>-0.00168437951736664</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0114532976874582</v>
+        <v>-0.0114532976874635</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.144035720109944</v>
+        <v>-0.143816179087459</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0474459417477036</v>
+        <v>0.0472264007252221</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0168104952337416</v>
+        <v>0.0167327100075152</v>
       </c>
       <c r="O3" t="n">
         <v>-0.048141643379644</v>
@@ -599,19 +599,19 @@
         <v>-0.0956576426778639</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0132881929407395</v>
+        <v>0.0135550494638307</v>
       </c>
       <c r="R3" t="n">
-        <v>0.193191113374414</v>
+        <v>0.193191113374404</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39899236527069</v>
+        <v>1.42562520364117</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.662649090799363</v>
+        <v>-0.688598753514341</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.234782132511107</v>
+        <v>-0.243976315729267</v>
       </c>
       <c r="V3" t="n">
         <v>-0.615456768307723</v>
@@ -628,19 +628,19 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>0.20134895862656</v>
+        <v>0.201979483112953</v>
       </c>
       <c r="D4" t="n">
         <v>24.6952947845805</v>
       </c>
       <c r="E4" t="n">
-        <v>14.0340224162712</v>
+        <v>14.0779699729728</v>
       </c>
       <c r="F4" t="n">
-        <v>55.6659775837288</v>
+        <v>55.6220300270272</v>
       </c>
       <c r="G4" t="n">
-        <v>20.4549228967293</v>
+        <v>20.4393519086689</v>
       </c>
       <c r="H4" t="n">
         <v>92.5</v>
@@ -649,19 +649,19 @@
         <v>87.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000388814466663071</v>
+        <v>0.000388918634425459</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0121840250522691</v>
+        <v>0.00343791857358156</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0345399438414731</v>
+        <v>0.0345705908528204</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00256390801038364</v>
+        <v>0.00253326099904072</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000908414119324519</v>
+        <v>0.000897555626085733</v>
       </c>
       <c r="O4" t="n">
         <v>0.0246019429075304</v>
@@ -670,19 +670,19 @@
         <v>-0.0431238042808602</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0269462175459613</v>
+        <v>-0.0267419862248208</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.674945701618412</v>
+        <v>-0.674945701618416</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.36656468444116</v>
+        <v>-2.35318104393009</v>
       </c>
       <c r="T4" t="n">
-        <v>0.284966919996343</v>
+        <v>0.271583279485291</v>
       </c>
       <c r="U4" t="n">
-        <v>0.100966170633622</v>
+        <v>0.0962242345114852</v>
       </c>
       <c r="V4" t="n">
         <v>-3.88454323169228</v>
@@ -702,7 +702,7 @@
         <v>0.200835796131606</v>
       </c>
       <c r="D5" t="n">
-        <v>24.5680254374524</v>
+        <v>25.8330183925422</v>
       </c>
       <c r="E5" t="n">
         <v>14.6434863089439</v>
@@ -720,19 +720,19 @@
         <v>87.5555555555556</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.000987020693620416</v>
+        <v>-0.000987020693620444</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00474882800209997</v>
+        <v>-0.0201758944318478</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0832806224342422</v>
+        <v>-0.0832806224342608</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0263361779897942</v>
+        <v>0.0263361779898119</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00933112882291454</v>
+        <v>0.00933112882293052</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -741,19 +741,19 @@
         <v>-0.284722222222236</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.000513162494953784</v>
+        <v>-0.00114368698134704</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.127269347128092</v>
+        <v>1.13772360796168</v>
       </c>
       <c r="S5" t="n">
-        <v>0.609463892672681</v>
+        <v>0.565516335971115</v>
       </c>
       <c r="T5" t="n">
-        <v>2.60164721843844</v>
+        <v>2.64559477514</v>
       </c>
       <c r="U5" t="n">
-        <v>0.921785437371895</v>
+        <v>0.937356425432291</v>
       </c>
       <c r="V5" t="n">
         <v>1.50000000000001</v>
@@ -773,13 +773,13 @@
         <v>0.20722550173706</v>
       </c>
       <c r="D6" t="n">
-        <v>25.0983317667637</v>
+        <v>25.246556054578</v>
       </c>
       <c r="E6" t="n">
-        <v>15.128548966064</v>
+        <v>15.1285489660641</v>
       </c>
       <c r="F6" t="n">
-        <v>57.864947907751</v>
+        <v>57.8649479077509</v>
       </c>
       <c r="G6" t="n">
         <v>21.2340365319412</v>
@@ -791,10 +791,10 @@
         <v>88.9399763389519</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000135699513390097</v>
+        <v>0.000135699513390125</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00454571966837669</v>
+        <v>-0.00668202938151019</v>
       </c>
       <c r="L6" t="n">
         <v>0.0104607424827901</v>
@@ -803,7 +803,7 @@
         <v>-0.00793167657759852</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.00281025955838743</v>
+        <v>-0.00281025955839098</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -812,19 +812,19 @@
         <v>0.00397837565660097</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00638970560545429</v>
+        <v>0.00638970560545427</v>
       </c>
       <c r="R6" t="n">
-        <v>0.530306329311312</v>
+        <v>-0.586462337964139</v>
       </c>
       <c r="S6" t="n">
-        <v>0.485062657120135</v>
+        <v>0.485062657120148</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.40267689441626</v>
+        <v>-0.402676894416274</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.142671802159956</v>
+        <v>-0.142671802160013</v>
       </c>
       <c r="V6" t="n">
         <v>-0.000000000000014210854715202</v>
@@ -841,10 +841,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>0.219918549416866</v>
+        <v>0.219918549416867</v>
       </c>
       <c r="D7" t="n">
-        <v>25.4113641085098</v>
+        <v>25.3510814484079</v>
       </c>
       <c r="E7" t="n">
         <v>16.0983347396554</v>
@@ -853,7 +853,7 @@
         <v>57.0869598819288</v>
       </c>
       <c r="G7" t="n">
-        <v>20.9583888470553</v>
+        <v>20.9583888470552</v>
       </c>
       <c r="H7" t="n">
         <v>94.8054474283113</v>
@@ -862,16 +862,16 @@
         <v>90.6545478908611</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000137784968497173</v>
+        <v>0.000137784968497159</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00360887428024803</v>
+        <v>0.0035207146101861</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0103922116088118</v>
+        <v>0.0103922116088135</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.00894461043509764</v>
+        <v>-0.0089446104351083</v>
       </c>
       <c r="N7" t="n">
         <v>-0.00316915052264122</v>
@@ -883,19 +883,19 @@
         <v>0.0291875926929066</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0126930476798062</v>
+        <v>0.0126930476798063</v>
       </c>
       <c r="R7" t="n">
-        <v>0.313032341746084</v>
+        <v>0.104525393829899</v>
       </c>
       <c r="S7" t="n">
-        <v>0.969785773591322</v>
+        <v>0.969785773591308</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.777988025822111</v>
+        <v>-0.777988025822097</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.27564768488595</v>
+        <v>-0.275647684885957</v>
       </c>
       <c r="V7" t="n">
         <v>0.805447428311339</v>
@@ -915,7 +915,7 @@
         <v>0.231411429587561</v>
       </c>
       <c r="D8" t="n">
-        <v>25.7199161577168</v>
+        <v>25.6914748173652</v>
       </c>
       <c r="E8" t="n">
         <v>16.9435914849201</v>
@@ -924,7 +924,7 @@
         <v>56.2688636848093</v>
       </c>
       <c r="G8" t="n">
-        <v>20.6685305005702</v>
+        <v>20.6685305005701</v>
       </c>
       <c r="H8" t="n">
         <v>95.9269610166363</v>
@@ -933,10 +933,10 @@
         <v>92.9454095664254</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000106455502027938</v>
+        <v>0.000106455502027925</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00279495988479006</v>
+        <v>0.00334567299912081</v>
       </c>
       <c r="L8" t="n">
         <v>0.00751173057637899</v>
@@ -954,19 +954,19 @@
         <v>0.0133464589940786</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0114928801706945</v>
+        <v>0.0114928801706946</v>
       </c>
       <c r="R8" t="n">
-        <v>0.308552049207005</v>
+        <v>0.340393368957219</v>
       </c>
       <c r="S8" t="n">
-        <v>0.84525674526472</v>
+        <v>0.845256745264695</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.818096197119544</v>
+        <v>-0.818096197119516</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.289858346485097</v>
+        <v>-0.289858346485076</v>
       </c>
       <c r="V8" t="n">
         <v>1.121513588325</v>
@@ -1004,19 +1004,19 @@
         <v>89.7685</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000520676696770805</v>
+        <v>0.000520676696770889</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0496031746031758</v>
+        <v>0.0496031746031775</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0712504687602031</v>
+        <v>0.0712504687602049</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0687495312397992</v>
+        <v>0.0687495312397957</v>
       </c>
       <c r="N9" t="n">
-        <v>0.024358535728382</v>
+        <v>0.0243585357283891</v>
       </c>
       <c r="O9" t="n">
         <v>0.186</v>
@@ -1025,19 +1025,19 @@
         <v>0.150666666666673</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00460741614717258</v>
+        <v>0.00460741614717244</v>
       </c>
       <c r="R9" t="n">
-        <v>0.125995123462332</v>
+        <v>0.154436463813965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.274052632841393</v>
+        <v>0.274052632841414</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.539007802570779</v>
+        <v>-0.539007802570801</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.190974986738514</v>
+        <v>-0.190974986738475</v>
       </c>
       <c r="V9" t="n">
         <v>-1.60296101663631</v>
@@ -1054,19 +1054,19 @@
         <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>0.22117937167196</v>
+        <v>0.221355414450014</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1189485319735</v>
+        <v>26.1189485319734</v>
       </c>
       <c r="E10" t="n">
-        <v>16.3322643832591</v>
+        <v>16.3457977224767</v>
       </c>
       <c r="F10" t="n">
-        <v>57.082276084131</v>
+        <v>57.0628811999067</v>
       </c>
       <c r="G10" t="n">
-        <v>20.9567293381984</v>
+        <v>20.9498575679942</v>
       </c>
       <c r="H10" t="n">
         <v>95.5</v>
@@ -1075,19 +1075,19 @@
         <v>92.9344005931585</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000127271474076124</v>
+        <v>0.000129777866718819</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0067254568818722</v>
+        <v>0.00672545688187398</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0140011116094776</v>
+        <v>0.0141941366539555</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00507971521514605</v>
+        <v>0.00487582652031904</v>
       </c>
       <c r="N10" t="n">
-        <v>0.00179978571965478</v>
+        <v>0.00172754624444416</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1096,19 +1096,19 @@
         <v>0.0254706811979304</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0148394740627738</v>
+        <v>-0.0146634312847199</v>
       </c>
       <c r="R10" t="n">
-        <v>0.273037250794324</v>
+        <v>0.273037250794289</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.885379734502347</v>
+        <v>-0.871846395284784</v>
       </c>
       <c r="T10" t="n">
-        <v>1.35242020189252</v>
+        <v>1.33302531766818</v>
       </c>
       <c r="U10" t="n">
-        <v>0.479173824366679</v>
+        <v>0.472302054162519</v>
       </c>
       <c r="V10" t="n">
         <v>1.17599999999996</v>
@@ -1125,19 +1125,19 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>0.239438196209441</v>
+        <v>0.239850065473901</v>
       </c>
       <c r="D11" t="n">
         <v>26.8232469545806</v>
       </c>
       <c r="E11" t="n">
-        <v>18.1518036574468</v>
+        <v>18.1834318267649</v>
       </c>
       <c r="F11" t="n">
-        <v>57.454560088542</v>
+        <v>57.4200471845117</v>
       </c>
       <c r="G11" t="n">
-        <v>21.0886326844324</v>
+        <v>21.0764044729705</v>
       </c>
       <c r="H11" t="n">
         <v>95.5</v>
@@ -1146,19 +1146,19 @@
         <v>94.7381232941868</v>
       </c>
       <c r="J11" t="n">
-        <v>0.000201741406641059</v>
+        <v>0.000204340366150496</v>
       </c>
       <c r="K11" t="n">
         <v>0.00710182553384442</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0195842419735275</v>
+        <v>0.0197823165465962</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00334122247726043</v>
+        <v>0.00319994020590642</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00118382315662302</v>
+        <v>0.00113376566252299</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1167,19 +1167,19 @@
         <v>0.0153742583913754</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0182588245374817</v>
+        <v>0.0184946510238869</v>
       </c>
       <c r="R11" t="n">
-        <v>0.704298422607156</v>
+        <v>0.704298422607195</v>
       </c>
       <c r="S11" t="n">
-        <v>1.81953927418765</v>
+        <v>1.83763410428817</v>
       </c>
       <c r="T11" t="n">
-        <v>0.372284004410979</v>
+        <v>0.357165984605047</v>
       </c>
       <c r="U11" t="n">
-        <v>0.131903346234051</v>
+        <v>0.126546904976262</v>
       </c>
       <c r="V11" t="n">
         <v>0.000000000000014210854715202</v>
@@ -1196,19 +1196,19 @@
         <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>0.236110951675369</v>
+        <v>0.236744391767828</v>
       </c>
       <c r="D12" t="n">
         <v>26.6216200526653</v>
       </c>
       <c r="E12" t="n">
-        <v>17.7474110379338</v>
+        <v>17.7949228718604</v>
       </c>
       <c r="F12" t="n">
-        <v>57.3895163446812</v>
+        <v>57.338590267411</v>
       </c>
       <c r="G12" t="n">
-        <v>21.065587140264</v>
+        <v>21.0475436038162</v>
       </c>
       <c r="H12" t="n">
         <v>96.8728301522479</v>
@@ -1217,19 +1217,19 @@
         <v>94.1413876869057</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.000263870645578049</v>
+        <v>-0.000262198946492445</v>
       </c>
       <c r="K12" t="n">
         <v>-0.0126002328366184</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0296052446845785</v>
+        <v>-0.0294853428692328</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.00598920302468642</v>
+        <v>-0.0054434457088135</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.00212202488119573</v>
+        <v>-0.0019286584852658</v>
       </c>
       <c r="O12" t="n">
         <v>0.0339951761939261</v>
@@ -1238,19 +1238,19 @@
         <v>-0.0365588526271097</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00332724453407246</v>
+        <v>-0.0031056737060729</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.201626901915283</v>
+        <v>-0.201626901915262</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.404392619512929</v>
+        <v>-0.388508954904452</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0650437438608265</v>
+        <v>-0.0814569171006951</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.023045544168415</v>
+        <v>-0.0288608691542152</v>
       </c>
       <c r="V12" t="n">
         <v>1.3728301522479</v>
@@ -1267,19 +1267,19 @@
         <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.224194444379972</v>
+        <v>0.224791637421506</v>
       </c>
       <c r="D13" t="n">
         <v>26.1599108190556</v>
       </c>
       <c r="E13" t="n">
-        <v>16.5800392999991</v>
+        <v>16.6244293466461</v>
       </c>
       <c r="F13" t="n">
-        <v>57.2536929957035</v>
+        <v>57.3205488492043</v>
       </c>
       <c r="G13" t="n">
-        <v>21.0174637881602</v>
+        <v>21.0411513779777</v>
       </c>
       <c r="H13" t="n">
         <v>96.6446309268737</v>
@@ -1288,19 +1288,19 @@
         <v>92.3412006616561</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.000113904129032671</v>
+        <v>-0.000114407056922797</v>
       </c>
       <c r="K13" t="n">
         <v>-0.00374612654075968</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.00930468722953037</v>
+        <v>-0.00935952614951674</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.00126838031911092</v>
+        <v>0.0000242272785264674</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.000449397788800709</v>
+        <v>0.00000858392804836683</v>
       </c>
       <c r="O13" t="n">
         <v>-0.00737464759258444</v>
@@ -1309,19 +1309,19 @@
         <v>-0.0158846985951016</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0119165072953965</v>
+        <v>-0.0119527543463213</v>
       </c>
       <c r="R13" t="n">
         <v>-0.461709233609703</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.16737173793474</v>
+        <v>-1.17049352521427</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.135823348977738</v>
+        <v>-0.0180414182067707</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04812335210379</v>
+        <v>-0.0063922258385567</v>
       </c>
       <c r="V13" t="n">
         <v>-0.228199225374226</v>
@@ -1338,19 +1338,19 @@
         <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>0.213225568434914</v>
+        <v>0.213769836419686</v>
       </c>
       <c r="D14" t="n">
         <v>25.8271420529343</v>
       </c>
       <c r="E14" t="n">
-        <v>15.7083633020509</v>
+        <v>15.7470584846477</v>
       </c>
       <c r="F14" t="n">
-        <v>57.1861624281508</v>
+        <v>57.3233171983635</v>
       </c>
       <c r="G14" t="n">
-        <v>20.9935371414933</v>
+        <v>21.0421322273113</v>
       </c>
       <c r="H14" t="n">
         <v>95.8316812500155</v>
@@ -1359,19 +1359,19 @@
         <v>90.8419938608137</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.000135861332917653</v>
+        <v>-0.000136550616492911</v>
       </c>
       <c r="K14" t="n">
         <v>-0.00402140929794292</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0113923103207023</v>
+        <v>-0.0114591307603025</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0000422847181766883</v>
+        <v>0.0000366454509546088</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0000149818304215898</v>
+        <v>0.0000129837907287822</v>
       </c>
       <c r="O14" t="n">
         <v>-0.00953055911669054</v>
@@ -1380,19 +1380,19 @@
         <v>-0.0189244659550667</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0109688759450583</v>
+        <v>-0.0110218010018199</v>
       </c>
       <c r="R14" t="n">
         <v>-0.332768766121326</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.87167599794819</v>
+        <v>-0.877370861998408</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0675305675526516</v>
+        <v>0.00276834915920432</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0239266466668795</v>
+        <v>0.000980849333643619</v>
       </c>
       <c r="V14" t="n">
         <v>-0.812949676858182</v>
@@ -1409,19 +1409,19 @@
         <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>0.19788644440633</v>
+        <v>0.198352907490676</v>
       </c>
       <c r="D15" t="n">
         <v>25.3454277913285</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2265907259833</v>
+        <v>14.2594566745013</v>
       </c>
       <c r="F15" t="n">
-        <v>57.3083446722623</v>
+        <v>57.3272237594352</v>
       </c>
       <c r="G15" t="n">
-        <v>21.0368273356939</v>
+        <v>21.0435163546752</v>
       </c>
       <c r="H15" t="n">
         <v>95.085056852645</v>
@@ -1430,19 +1430,19 @@
         <v>88.5586296921174</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.000209953537461796</v>
+        <v>-0.000211003275102831</v>
       </c>
       <c r="K15" t="n">
         <v>-0.00701965391404258</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.022713403232153</v>
+        <v>-0.022771195339585</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0029011320251584</v>
+        <v>0.0000492429249518977</v>
       </c>
       <c r="N15" t="n">
-        <v>0.00102789541707615</v>
+        <v>0.0000174471814613497</v>
       </c>
       <c r="O15" t="n">
         <v>-0.00591694914231766</v>
@@ -1451,19 +1451,19 @@
         <v>-0.033118926460034</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.015339124028584</v>
+        <v>-0.0154169289290108</v>
       </c>
       <c r="R15" t="n">
         <v>-0.481714261605802</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.48177257606761</v>
+        <v>-1.48760181014645</v>
       </c>
       <c r="T15" t="n">
-        <v>0.122182244111478</v>
+        <v>0.00390656107175857</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0432901942005266</v>
+        <v>0.00138412736388815</v>
       </c>
       <c r="V15" t="n">
         <v>-0.74662439737051</v>
@@ -1480,19 +1480,19 @@
         <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>0.197788010978955</v>
+        <v>0.198456541483889</v>
       </c>
       <c r="D16" t="n">
         <v>25.6167190268245</v>
       </c>
       <c r="E16" t="n">
-        <v>14.3026595413271</v>
+        <v>14.3511732703563</v>
       </c>
       <c r="F16" t="n">
-        <v>57.9979682399825</v>
+        <v>57.9494545109533</v>
       </c>
       <c r="G16" t="n">
-        <v>21.2811667516944</v>
+        <v>21.2639779304681</v>
       </c>
       <c r="H16" t="n">
         <v>95</v>
@@ -1501,19 +1501,19 @@
         <v>89.164041640178</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000203111812912354</v>
+        <v>0.00021218957722588</v>
       </c>
       <c r="K16" t="n">
         <v>0.0953874543566133</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0678028744952668</v>
+        <v>0.0686271528634599</v>
       </c>
       <c r="M16" t="n">
-        <v>0.201418676680827</v>
+        <v>0.200594398312639</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0713643270552851</v>
+        <v>0.0710722783137285</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1522,19 +1522,19 @@
         <v>0.258338366179274</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.0000984334273747278</v>
+        <v>0.000103633993213781</v>
       </c>
       <c r="R16" t="n">
         <v>0.271291235496008</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0760688153438132</v>
+        <v>0.0917165958550346</v>
       </c>
       <c r="T16" t="n">
-        <v>0.689623567720183</v>
+        <v>0.622230751518025</v>
       </c>
       <c r="U16" t="n">
-        <v>0.24433941600056</v>
+        <v>0.220461575792932</v>
       </c>
       <c r="V16" t="n">
         <v>-0.085056852644982</v>
@@ -1551,19 +1551,19 @@
         <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>0.20337674887538</v>
+        <v>0.203498885609441</v>
       </c>
       <c r="D17" t="n">
         <v>25.2894073078861</v>
       </c>
       <c r="E17" t="n">
-        <v>14.5211170074432</v>
+        <v>14.5296216600333</v>
       </c>
       <c r="F17" t="n">
-        <v>56.8557061783346</v>
+        <v>56.8472015257444</v>
       </c>
       <c r="G17" t="n">
-        <v>20.876453719648</v>
+        <v>20.8734404498811</v>
       </c>
       <c r="H17" t="n">
         <v>95</v>
@@ -1572,19 +1572,19 @@
         <v>88.6004509866667</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000408800597994613</v>
+        <v>0.000399419415408386</v>
       </c>
       <c r="K17" t="n">
         <v>0.0240151260213075</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0427087947379476</v>
+        <v>0.0420596051363695</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0250714969445909</v>
+        <v>0.025720686546169</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00888304171789756</v>
+        <v>0.00911305504045146</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1593,19 +1593,19 @@
         <v>0.0659938895238099</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.00558873789642494</v>
+        <v>0.00504234412555107</v>
       </c>
       <c r="R17" t="n">
         <v>-0.327311718938407</v>
       </c>
       <c r="S17" t="n">
-        <v>0.218457466116032</v>
+        <v>0.178448389677021</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.14226206164784</v>
+        <v>-1.10225298520883</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.40471303204637</v>
+        <v>-0.390537480587025</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1622,19 +1622,19 @@
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>0.221741652836584</v>
+        <v>0.221995734006071</v>
       </c>
       <c r="D18" t="n">
         <v>28.0666561555177</v>
       </c>
       <c r="E18" t="n">
-        <v>17.5660447664379</v>
+        <v>17.5862217263137</v>
       </c>
       <c r="F18" t="n">
-        <v>61.6492855668954</v>
+        <v>61.6291086070196</v>
       </c>
       <c r="G18" t="n">
-        <v>22.5748591152549</v>
+        <v>22.5677102490857</v>
       </c>
       <c r="H18" t="n">
         <v>95</v>
@@ -1643,19 +1643,19 @@
         <v>92.3364793333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000163987057477347</v>
+        <v>0.000166760857632869</v>
       </c>
       <c r="K18" t="n">
         <v>-0.015563114134542</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00281407000696987</v>
+        <v>0.00301456248427634</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0467394033403039</v>
+        <v>-0.0469398958176086</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0165601627481209</v>
+        <v>-0.0166311989149719</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1664,19 +1664,19 @@
         <v>0.0138773333333333</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0183649039612031</v>
+        <v>0.0184968483966302</v>
       </c>
       <c r="R18" t="n">
         <v>2.7772488476316</v>
       </c>
       <c r="S18" t="n">
-        <v>3.04492775899474</v>
+        <v>3.05660006628034</v>
       </c>
       <c r="T18" t="n">
-        <v>4.79357938856081</v>
+        <v>4.78190708127521</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69840539560682</v>
+        <v>1.69426979920462</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1693,19 +1693,19 @@
         <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>0.229165873348694</v>
+        <v>0.229624311515166</v>
       </c>
       <c r="D19" t="n">
         <v>28.2855672440437</v>
       </c>
       <c r="E19" t="n">
-        <v>18.2958109563309</v>
+        <v>18.3324088473449</v>
       </c>
       <c r="F19" t="n">
-        <v>61.5396692682784</v>
+        <v>61.5030713772644</v>
       </c>
       <c r="G19" t="n">
-        <v>22.5360211409716</v>
+        <v>22.5230542011283</v>
       </c>
       <c r="H19" t="n">
         <v>95</v>
@@ -1714,19 +1714,19 @@
         <v>95.4147946777344</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.000150161392570375</v>
+        <v>-0.00014968510284398</v>
       </c>
       <c r="K19" t="n">
         <v>-0.00991709445380806</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0180347418945246</v>
+        <v>-0.0180092017353477</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.00862128274490104</v>
+        <v>-0.0086468229040797</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.003054592809276</v>
+        <v>-0.00306364190195652</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1735,19 +1735,19 @@
         <v>0.0422760667067266</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.00742422051211014</v>
+        <v>0.00762857750909515</v>
       </c>
       <c r="R19" t="n">
         <v>0.218911088525953</v>
       </c>
       <c r="S19" t="n">
-        <v>0.729766189893041</v>
+        <v>0.746187121031248</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.109616298617006</v>
+        <v>-0.126037229755212</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0388379742832292</v>
+        <v>-0.0446560479574529</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1764,19 +1764,19 @@
         <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>0.233671549779525</v>
+        <v>0.23410619322823</v>
       </c>
       <c r="D20" t="n">
         <v>27.9606744786907</v>
       </c>
       <c r="E20" t="n">
-        <v>18.4719424360782</v>
+        <v>18.5063194382941</v>
       </c>
       <c r="F20" t="n">
-        <v>60.6231124691518</v>
+        <v>60.5887354669359</v>
       </c>
       <c r="G20" t="n">
-        <v>22.2112773771087</v>
+        <v>22.1990973167998</v>
       </c>
       <c r="H20" t="n">
         <v>95</v>
@@ -1785,19 +1785,19 @@
         <v>95.8266371779907</v>
       </c>
       <c r="J20" t="n">
-        <v>0.000114461438902758</v>
+        <v>0.00011418054866047</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.00210283295441904</v>
+        <v>-0.00210283295442082</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00926661597886635</v>
+        <v>0.00924477494498355</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.00769134139752481</v>
+        <v>-0.00766950036364022</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0027251067876719</v>
+        <v>-0.00271736832612035</v>
       </c>
       <c r="O20" t="n">
         <v>-0.000000000000007105427357601</v>
@@ -1806,19 +1806,19 @@
         <v>-0.00558876184142321</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.00450567643083144</v>
+        <v>0.00448188171306427</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.324892765352942</v>
+        <v>-0.324892765352949</v>
       </c>
       <c r="S20" t="n">
-        <v>0.176131479747301</v>
+        <v>0.173910590949195</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.916556799126646</v>
+        <v>-0.914335910328546</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.324743763862902</v>
+        <v>-0.32395688432846</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -1835,19 +1835,19 @@
         <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244643030974765</v>
+        <v>0.245050756564305</v>
       </c>
       <c r="D21" t="n">
         <v>27.7543093401667</v>
       </c>
       <c r="E21" t="n">
-        <v>19.3715120486206</v>
+        <v>19.4038255504603</v>
       </c>
       <c r="F21" t="n">
-        <v>59.921301579738</v>
+        <v>59.8889880778983</v>
       </c>
       <c r="G21" t="n">
-        <v>21.9626198907801</v>
+        <v>21.9511709459673</v>
       </c>
       <c r="H21" t="n">
         <v>95</v>
@@ -1856,19 +1856,19 @@
         <v>95.1032968112145</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000102865254607856</v>
+        <v>0.000102566009833507</v>
       </c>
       <c r="K21" t="n">
         <v>-0.00250081253350487</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00791855016489507</v>
+        <v>0.00789476546282764</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.00829239832194517</v>
+        <v>-0.00826861361987952</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.00293806629887605</v>
+        <v>-0.00292963917937961</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1877,19 +1877,19 @@
         <v>-0.00923225237303171</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0109714811952399</v>
+        <v>0.0109445633360744</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.206365138524042</v>
+        <v>-0.206365138524056</v>
       </c>
       <c r="S21" t="n">
-        <v>0.899569612542368</v>
+        <v>0.897506112166202</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.701810889413764</v>
+        <v>-0.699747389037597</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.248657486328593</v>
+        <v>-0.247926370832527</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -1906,19 +1906,19 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.248769550940614</v>
+        <v>0.249150634981426</v>
       </c>
       <c r="D22" t="n">
         <v>27.4860974859895</v>
       </c>
       <c r="E22" t="n">
-        <v>19.5077116637088</v>
+        <v>19.5376316640513</v>
       </c>
       <c r="F22" t="n">
-        <v>58.9899478993584</v>
+        <v>58.9600278990158</v>
       </c>
       <c r="G22" t="n">
-        <v>21.6326334677432</v>
+        <v>21.6220325605923</v>
       </c>
       <c r="H22" t="n">
         <v>95</v>
@@ -1927,19 +1927,19 @@
         <v>94.3091443336706</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0000314377712700153</v>
+        <v>-0.0000317257415953509</v>
       </c>
       <c r="K22" t="n">
         <v>-0.00357184803073096</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.00716065780632036</v>
+        <v>-0.00719079607959472</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0131000744540515</v>
+        <v>-0.0130699361807807</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.00464146628899265</v>
+        <v>-0.00463078804590999</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -1948,19 +1948,19 @@
         <v>-0.00755066242081881</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.00412651996584942</v>
+        <v>0.00409987841712156</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.268211854177178</v>
+        <v>-0.268211854177181</v>
       </c>
       <c r="S22" t="n">
-        <v>0.136199615088188</v>
+        <v>0.133806113591</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.931353680379644</v>
+        <v>-0.928960178882448</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.329986423036985</v>
+        <v>-0.329138385375018</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -1977,19 +1977,19 @@
         <v>24</v>
       </c>
       <c r="C23" t="n">
-        <v>0.218089510312907</v>
+        <v>0.218543372814369</v>
       </c>
       <c r="D23" t="n">
         <v>25.8665485820957</v>
       </c>
       <c r="E23" t="n">
-        <v>15.9214508306061</v>
+        <v>15.9545865515424</v>
       </c>
       <c r="F23" t="n">
-        <v>57.0842958875009</v>
+        <v>57.0511601665646</v>
       </c>
       <c r="G23" t="n">
-        <v>20.9574449714785</v>
+        <v>20.9457047075413</v>
       </c>
       <c r="H23" t="n">
         <v>95</v>
@@ -1998,19 +1998,19 @@
         <v>91.0101562321969</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.000284418145779675</v>
+        <v>-0.000284318482313028</v>
       </c>
       <c r="K23" t="n">
         <v>0.00293218917160409</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.019271303470342</v>
+        <v>-0.0192592283424897</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0275471141882839</v>
+        <v>0.0275350390604245</v>
       </c>
       <c r="N23" t="n">
-        <v>0.00976017367781878</v>
+        <v>0.00975589535870647</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2019,19 +2019,19 @@
         <v>0.0127035386249545</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.0306800406277075</v>
+        <v>-0.0306072621670569</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.6195489038938</v>
+        <v>-1.61954890389378</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.58626083310267</v>
+        <v>-3.58304511250891</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.90565201185752</v>
+        <v>-1.90886773245128</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.675188496264656</v>
+        <v>-0.676327853050953</v>
       </c>
       <c r="V23" t="n">
         <v>-0.000000000000014210854715202</v>
@@ -2090,19 +2090,19 @@
         <v>0.00650892823429672</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.00855679000878976</v>
+        <v>-0.00901065251025207</v>
       </c>
       <c r="R24" t="n">
         <v>0.41907284043954</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.355215387992592</v>
+        <v>-0.388351108928903</v>
       </c>
       <c r="T24" t="n">
-        <v>1.30818380766002</v>
+        <v>1.34131952859633</v>
       </c>
       <c r="U24" t="n">
-        <v>0.463500498745731</v>
+        <v>0.475240762682898</v>
       </c>
       <c r="V24" t="n">
         <v>0.0279060167261065</v>
@@ -3693,7 +3693,7 @@
         <v>59.4501491847233</v>
       </c>
       <c r="G47" t="n">
-        <v>21.7956866442473</v>
+        <v>21.7956866442472</v>
       </c>
       <c r="H47" t="n">
         <v>97.604456267978</v>
@@ -3735,7 +3735,7 @@
         <v>0.548058165076874</v>
       </c>
       <c r="U47" t="n">
-        <v>0.194181606107257</v>
+        <v>0.194181606107222</v>
       </c>
       <c r="V47" t="n">
         <v>-2.11957678987321</v>
@@ -3764,7 +3764,7 @@
         <v>59.566898945139</v>
       </c>
       <c r="G48" t="n">
-        <v>21.8370520638957</v>
+        <v>21.8370520638956</v>
       </c>
       <c r="H48" t="n">
         <v>97.8798270769658</v>
@@ -3806,7 +3806,7 @@
         <v>0.116749760415651</v>
       </c>
       <c r="U48" t="n">
-        <v>0.0413654196483897</v>
+        <v>0.0413654196483755</v>
       </c>
       <c r="V48" t="n">
         <v>0.275370808987788</v>
@@ -3877,7 +3877,7 @@
         <v>-0.490672922173857</v>
       </c>
       <c r="U49" t="n">
-        <v>-0.17384953308321</v>
+        <v>-0.173849533083164</v>
       </c>
       <c r="V49" t="n">
         <v>1.08060144929397</v>
@@ -3948,7 +3948,7 @@
         <v>-0.293281641100151</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.103912146081381</v>
+        <v>-0.103912146081377</v>
       </c>
       <c r="V50" t="n">
         <v>-0.707533270183376</v>
@@ -3983,7 +3983,7 @@
         <v>98</v>
       </c>
       <c r="I51" t="n">
-        <v>99.7394545022698</v>
+        <v>99.7392791496304</v>
       </c>
       <c r="J51" t="n">
         <v>-0.0000145271580486439</v>
@@ -3995,7 +3995,7 @@
         <v>0.000321665299592766</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0052399486814636</v>
+        <v>0.00523994868146715</v>
       </c>
       <c r="N51" t="n">
         <v>0.00185655778112981</v>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.000528366172389383</v>
+        <v>-0.000546221152212922</v>
       </c>
       <c r="Q51" t="n">
         <v>0.00342810182675496</v>
@@ -4025,7 +4025,7 @@
         <v>-0.252895256076386</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.38938111891747</v>
+        <v>-0.389556471556801</v>
       </c>
     </row>
     <row r="52">
@@ -4054,7 +4054,7 @@
         <v>98</v>
       </c>
       <c r="I52" t="n">
-        <v>99.7054344110844</v>
+        <v>99.7044642387315</v>
       </c>
       <c r="J52" t="n">
         <v>-0.0000159127211339927</v>
@@ -4066,7 +4066,7 @@
         <v>0.000372748429535719</v>
       </c>
       <c r="M52" t="n">
-        <v>0.00601359513091992</v>
+        <v>0.00601359513091637</v>
       </c>
       <c r="N52" t="n">
         <v>0.00213066720908373</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>-0.000324439251066622</v>
+        <v>-0.000281437965121256</v>
       </c>
       <c r="Q52" t="n">
         <v>-0.00183962954116845</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.034020091185397</v>
+        <v>-0.0348149108989304</v>
       </c>
     </row>
     <row r="53">
@@ -4107,67 +4107,67 @@
         <v>26</v>
       </c>
       <c r="C53" t="n">
-        <v>0.279392455601603</v>
+        <v>0.279953060074281</v>
       </c>
       <c r="D53" t="n">
-        <v>29.1149235302441</v>
+        <v>29.1811006222212</v>
       </c>
       <c r="E53" t="n">
-        <v>22.950670435472</v>
+        <v>23.0483109935727</v>
       </c>
       <c r="F53" t="n">
-        <v>59.2142341378106</v>
+        <v>59.303371804106</v>
       </c>
       <c r="G53" t="n">
-        <v>21.7120999637935</v>
+        <v>21.743682186829</v>
       </c>
       <c r="H53" t="n">
-        <v>98.8327645913682</v>
+        <v>98.9341111418452</v>
       </c>
       <c r="I53" t="n">
-        <v>99.6146798134259</v>
+        <v>99.6315433363655</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0000296198657046276</v>
+        <v>0.0000380725977919549</v>
       </c>
       <c r="K53" t="n">
-        <v>0.00169979333141512</v>
+        <v>0.00269760418748533</v>
       </c>
       <c r="L53" t="n">
-        <v>0.00386091556888246</v>
+        <v>0.0053331290789469</v>
       </c>
       <c r="M53" t="n">
-        <v>0.00102091007054383</v>
+        <v>0.00236491792065152</v>
       </c>
       <c r="N53" t="n">
-        <v>0.000361717003452</v>
+        <v>0.000837910260999664</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0129448668503187</v>
+        <v>0.0144729589025658</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.00127545477117508</v>
+        <v>-0.00106409527710127</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.00175277224811954</v>
+        <v>0.00231337672079729</v>
       </c>
       <c r="R53" t="n">
-        <v>0.168424621698748</v>
+        <v>0.234601713675808</v>
       </c>
       <c r="S53" t="n">
-        <v>0.26369084823574</v>
+        <v>0.361331406336383</v>
       </c>
       <c r="T53" t="n">
-        <v>0.198173197932803</v>
+        <v>0.287310864228239</v>
       </c>
       <c r="U53" t="n">
-        <v>0.0702144267051992</v>
+        <v>0.101796649740702</v>
       </c>
       <c r="V53" t="n">
-        <v>0.832764591368218</v>
+        <v>0.934111141845165</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.0907545976584458</v>
+        <v>-0.0729209023659934</v>
       </c>
     </row>
     <row r="54">
@@ -4178,67 +4178,209 @@
         <v>23</v>
       </c>
       <c r="C54" t="n">
-        <v>0.282057322132758</v>
+        <v>0.281935064640735</v>
       </c>
       <c r="D54" t="n">
-        <v>29.265873015873</v>
+        <v>29.2497127617387</v>
       </c>
       <c r="E54" t="n">
-        <v>23.2979348081658</v>
+        <v>23.2753059218724</v>
       </c>
       <c r="F54" t="n">
-        <v>59.3020651918342</v>
+        <v>59.279083376859</v>
       </c>
       <c r="G54" t="n">
-        <v>21.7432192431385</v>
+        <v>21.7350765932748</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>99.9849410430534</v>
       </c>
       <c r="I54" t="n">
-        <v>99.5</v>
+        <v>99.4639759849595</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0000281044948902132</v>
+        <v>-0.000122347851072901</v>
       </c>
       <c r="K54" t="n">
-        <v>0.00171733036503241</v>
+        <v>-0.0162992214068005</v>
       </c>
       <c r="L54" t="n">
-        <v>0.00366855959483203</v>
+        <v>-0.0227510326582099</v>
       </c>
       <c r="M54" t="n">
-        <v>0.00118090061749854</v>
+        <v>-0.0232518898403455</v>
       </c>
       <c r="N54" t="n">
-        <v>0.000418402996558598</v>
+        <v>-0.00823833965431575</v>
       </c>
       <c r="O54" t="n">
-        <v>0.0121453076216937</v>
+        <v>-0.0150809057779639</v>
       </c>
       <c r="P54" t="n">
-        <v>-0.0012139739955046</v>
+        <v>-0.0366510384409082</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.00266486653115505</v>
+        <v>0.00198200456645437</v>
       </c>
       <c r="R54" t="n">
-        <v>0.150949485628921</v>
+        <v>0.0686121395175618</v>
       </c>
       <c r="S54" t="n">
-        <v>0.347264372693797</v>
+        <v>0.226994928299714</v>
       </c>
       <c r="T54" t="n">
-        <v>0.0878310540235816</v>
+        <v>-0.0242884272470008</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0311192793450665</v>
+        <v>-0.00860559355411183</v>
       </c>
       <c r="V54" t="n">
-        <v>1.16723540863178</v>
+        <v>1.05082990120827</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.114679813425937</v>
+        <v>-0.167567351405978</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.259256766671901</v>
+      </c>
+      <c r="D55" t="n">
+        <v>27.9044305113699</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20.2924562410301</v>
+      </c>
+      <c r="F55" t="n">
+        <v>58.1189694111622</v>
+      </c>
+      <c r="G55" t="n">
+        <v>21.324038481846</v>
+      </c>
+      <c r="H55" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>95.3094504277403</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0.0000011188211601898</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.0156917136265857</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.00570022797786152</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.017508440348184</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.00620338731157766</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-0.0133712461023592</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-0.0226782979688346</v>
+      </c>
+      <c r="R55" t="n">
+        <v>-1.34528225036879</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-2.98284968084227</v>
+      </c>
+      <c r="T55" t="n">
+        <v>-1.16011396569683</v>
+      </c>
+      <c r="U55" t="n">
+        <v>-0.411038111428834</v>
+      </c>
+      <c r="V55" t="n">
+        <v>-3.48494104305345</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-4.15452555721922</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.259235576565908</v>
+      </c>
+      <c r="D56" t="n">
+        <v>28.0257936507937</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20.5055341063634</v>
+      </c>
+      <c r="F56" t="n">
+        <v>58.5944658936366</v>
+      </c>
+      <c r="G56" t="n">
+        <v>21.492510875013</v>
+      </c>
+      <c r="H56" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>95</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0.000000665897515128577</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.00417502878074316</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.00631545183579618</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.0177007409812759</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.00627152103928452</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0.0130089513307041</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-0.0000211901059927744</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.121363139423771</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.213077865333275</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.475496482474419</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.16847239316699</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-0.30945042774033</v>
       </c>
     </row>
   </sheetData>
